--- a/EKG_Kalite_Yönetim_Sistemi/03_Hızlı Müdahale ve Problem Çözme/01_FR1 - Günlük Toplantı ve Görsel Yönetim/EKG-URT-PNO-02_uretim_performans_panosu.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/03_Hızlı Müdahale ve Problem Çözme/01_FR1 - Günlük Toplantı ve Görsel Yönetim/EKG-URT-PNO-02_uretim_performans_panosu.xlsx
@@ -885,7 +885,8 @@
   <pageSetup scale="100"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-URT-PNO-02&amp;C&amp;"Arial,Regular"&amp;11Üretim Performans Panosu</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 09.06.2026 | Revizyon: 17.09.2026
+Revizyon nedeni: Üretim panosundaki gereksiz risk alanları kaldırıldı; hesap, dönem, hedef ve aksiyon alanları düzenlendi.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>